--- a/basedatos_partidas/salida/descompuestos/CT-05-06-050.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-05-06-050.xlsx
@@ -539,10 +539,10 @@
         <v>0.13</v>
       </c>
       <c r="G10" t="n">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="H10" t="n">
-        <v>17.94</v>
+        <v>17.16</v>
       </c>
     </row>
     <row r="11">
@@ -565,10 +565,10 @@
         <v>26</v>
       </c>
       <c r="G11" t="n">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="H11" t="n">
-        <v>35.1</v>
+        <v>31.2</v>
       </c>
     </row>
     <row r="12">
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>93.92</v>
+        <v>89.23999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -1036,10 +1036,10 @@
         <v>1</v>
       </c>
       <c r="G33" t="n">
-        <v>137.35</v>
+        <v>132.67</v>
       </c>
       <c r="H33" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="34">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="G34" s="4" t="n"/>
       <c r="H34" s="5" t="n">
-        <v>138.72</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>

--- a/basedatos_partidas/salida/descompuestos/CT-05-06-050.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-05-06-050.xlsx
@@ -617,10 +617,10 @@
         <v>0.85</v>
       </c>
       <c r="G13" t="n">
-        <v>22</v>
+        <v>95</v>
       </c>
       <c r="H13" t="n">
-        <v>18.7</v>
+        <v>80.75</v>
       </c>
     </row>
     <row r="14">
@@ -643,10 +643,10 @@
         <v>0.6</v>
       </c>
       <c r="G14" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H14" t="n">
-        <v>8.4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -669,10 +669,10 @@
         <v>1.6</v>
       </c>
       <c r="G15" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="H15" t="n">
-        <v>8.960000000000001</v>
+        <v>8.640000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -695,10 +695,10 @@
         <v>0.8</v>
       </c>
       <c r="G16" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="H16" t="n">
-        <v>2.08</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="17">
@@ -721,10 +721,10 @@
         <v>0.55</v>
       </c>
       <c r="G17" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="H17" t="n">
-        <v>0.99</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="18">
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>89.23999999999999</v>
+        <v>154.69</v>
       </c>
     </row>
     <row r="20">
@@ -1036,10 +1036,10 @@
         <v>1</v>
       </c>
       <c r="G33" t="n">
-        <v>132.67</v>
+        <v>198.12</v>
       </c>
       <c r="H33" t="n">
-        <v>1.33</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="34">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="G34" s="4" t="n"/>
       <c r="H34" s="5" t="n">
-        <v>134</v>
+        <v>200.1</v>
       </c>
     </row>
   </sheetData>

--- a/basedatos_partidas/salida/descompuestos/CT-05-06-050.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-05-06-050.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H34"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -451,6 +451,20 @@
     <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Capítulo: 05 Estructuras</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Subcapítulo: Refuerzos y reparaciones estructurales</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
